--- a/exemple-ePrescription/ig/StructureDefinition-fr-cda-resultat-examens-de-biologie-element-clinique-pertinent.xlsx
+++ b/exemple-ePrescription/ig/StructureDefinition-fr-cda-resultat-examens-de-biologie-element-clinique-pertinent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T08:51:06+00:00</t>
+    <t>2026-05-06T11:50:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -5312,7 +5312,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
         <v>158</v>
       </c>
@@ -5331,7 +5331,7 @@
         <v>75</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>74</v>
@@ -5716,7 +5716,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
         <v>167</v>
       </c>
@@ -5731,13 +5731,13 @@
         <v>62</v>
       </c>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>74</v>
@@ -5819,7 +5819,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
         <v>170</v>
       </c>
@@ -5834,13 +5834,13 @@
         <v>171</v>
       </c>
       <c r="F32" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>74</v>
@@ -6128,7 +6128,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
         <v>183</v>
       </c>
@@ -6149,7 +6149,7 @@
         <v>75</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>74</v>
